--- a/tests/A01_pixell_test_plan_client.xlsx
+++ b/tests/A01_pixell_test_plan_client.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkwarkentin\Documents\Course Folders\2-Intermediate Software Development\Code\Assignments 2024 Spring\Assignment 1\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECD6C5C-0BF7-4659-811B-1D416A6C1BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02F27C92-EEC1-421A-AB1D-3450BDCB29D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D9DD509-55B1-455D-8036-16809AD15960}"/>
   </bookViews>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>Software Development Team - Unit Test Plan</t>
   </si>
@@ -191,6 +191,9 @@
     <t>Developer:</t>
   </si>
   <si>
+    <t>Rogine Mirando</t>
+  </si>
+  <si>
     <t>Class Name:</t>
   </si>
   <si>
@@ -221,46 +224,121 @@
     <t>Attributes set to input values.</t>
   </si>
   <si>
+    <t>all values are valid</t>
+  </si>
+  <si>
+    <t>int, string</t>
+  </si>
+  <si>
+    <t>1, Rogine, Mirando, rmirando2@rrc.ca</t>
+  </si>
+  <si>
     <t>Exception raised when invalid client number.</t>
   </si>
   <si>
+    <t>Client number must not be an integer type</t>
+  </si>
+  <si>
+    <t>Anything but an integer</t>
+  </si>
+  <si>
+    <t>Client number must be an integer</t>
+  </si>
+  <si>
     <t>Exception raised when blank first_name.</t>
   </si>
   <si>
+    <t>First name must be blank</t>
+  </si>
+  <si>
+    <t>An empty string</t>
+  </si>
+  <si>
+    <t>First name must be filled</t>
+  </si>
+  <si>
     <t>Exception raised when blank last_name.</t>
   </si>
   <si>
+    <t>Last name must be blank</t>
+  </si>
+  <si>
+    <t>Last name must be filled</t>
+  </si>
+  <si>
     <t>Email address set to default value when invalid.</t>
   </si>
   <si>
+    <t>Email address must be invalid</t>
+  </si>
+  <si>
+    <t>Invalid email address</t>
+  </si>
+  <si>
+    <t>Enter a valid email address</t>
+  </si>
+  <si>
     <t>client_number</t>
   </si>
   <si>
     <t>Returns client_number attribute.</t>
   </si>
   <si>
+    <t>Client number has an integer value</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>first_name</t>
   </si>
   <si>
     <t>Returns first_name attribute.</t>
   </si>
   <si>
+    <t>First name is not blank and a string</t>
+  </si>
+  <si>
+    <t>str</t>
+  </si>
+  <si>
+    <t>Rogine</t>
+  </si>
+  <si>
     <t>last_name</t>
   </si>
   <si>
     <t>Returns last_name attribute.</t>
   </si>
   <si>
+    <t>Last name is not blank and a string</t>
+  </si>
+  <si>
+    <t>Mirando</t>
+  </si>
+  <si>
     <t>email_address</t>
   </si>
   <si>
     <t>Returns email_address attribute.</t>
   </si>
   <si>
+    <t>Email address must be valid</t>
+  </si>
+  <si>
+    <t>rmirando2@rrc.ca</t>
+  </si>
+  <si>
     <t>__str__</t>
   </si>
   <si>
     <t>Returns string in expected format.</t>
+  </si>
+  <si>
+    <t>All conditions above met</t>
+  </si>
+  <si>
+    <t>Mirando, Rogine, [1] - rmirando2@rrc.ca</t>
   </si>
   <si>
     <t>Add more rows as necessary</t>
@@ -270,7 +348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +409,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -504,10 +590,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -534,6 +621,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -559,7 +649,8 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
@@ -1101,51 +1192,53 @@
       <c r="B2" s="2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1">
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1">
       <c r="B4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="C4" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="1"/>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="66" customHeight="1">
@@ -1154,14 +1247,20 @@
         <v>1</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="66" customHeight="1">
       <c r="A8" s="4"/>
@@ -1169,14 +1268,20 @@
         <v>2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="66" customHeight="1">
       <c r="A9" s="4"/>
@@ -1184,14 +1289,20 @@
         <v>3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="66" customHeight="1">
       <c r="A10" s="4"/>
@@ -1199,14 +1310,20 @@
         <v>4</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="66" customHeight="1">
       <c r="A11" s="4"/>
@@ -1214,84 +1331,120 @@
         <v>5</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="31.15" customHeight="1">
       <c r="B12" s="11">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="31.15" customHeight="1">
       <c r="B13" s="9">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="31.15" customHeight="1">
       <c r="B14" s="11">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="31.15" customHeight="1">
       <c r="B15" s="11">
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="31.15" customHeight="1">
       <c r="B16" s="9">
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="2:7" ht="31.15" customHeight="1">
       <c r="B17" s="11">
@@ -1414,14 +1567,14 @@
       <c r="G28" s="3"/>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1430,10 +1583,13 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="B30:G30"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G15" r:id="rId1" xr:uid="{DCFCD693-4988-4E8F-B5AB-1594855CC81B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>